--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_magallanes.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:15</t>
+    <t xml:space="preserve">2026-09-24 01:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -662,13 +662,13 @@
         <v>16</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.89</v>
+        <v>0.71</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="8">
@@ -685,13 +685,13 @@
         <v>16</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.52</v>
+        <v>0.21</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.32</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="9">
@@ -708,13 +708,13 @@
         <v>16</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.6</v>
+        <v>0.26</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.34</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -737,7 +737,7 @@
         <v>0.07</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="11">
@@ -757,10 +757,10 @@
         <v>0.65</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="12">
@@ -776,11 +776,15 @@
       <c r="D12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2" t="n">
+        <v>0.81</v>
+      </c>
       <c r="F12" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G12" s="2"/>
+        <v>0.11</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
@@ -795,11 +799,15 @@
       <c r="D13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F13" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="G13" s="2"/>
+      <c r="G13" s="2" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
@@ -841,10 +849,10 @@
         <v>-0.01</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="16">
@@ -861,13 +869,13 @@
         <v>16</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.56</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>-0.42</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="17">
@@ -884,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="18">
@@ -926,13 +934,13 @@
         <v>30</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.3</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="20">
@@ -949,13 +957,13 @@
         <v>30</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.06</v>
+        <v>0.02</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="21">
@@ -972,13 +980,13 @@
         <v>30</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.25</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0.13</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="22">
@@ -1090,13 +1098,13 @@
         <v>16</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.61</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="28">
@@ -1113,13 +1121,13 @@
         <v>16</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.21</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>-0.07</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="29">
@@ -1136,13 +1144,13 @@
         <v>16</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.27</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>-0.08</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="30">
@@ -1204,11 +1212,15 @@
       <c r="D32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E32" s="2"/>
+      <c r="E32" s="2" t="n">
+        <v>0.09</v>
+      </c>
       <c r="F32" s="2" t="n">
         <v>0.22</v>
       </c>
-      <c r="G32" s="2"/>
+      <c r="G32" s="2" t="n">
+        <v>-0.12</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
@@ -1223,11 +1235,15 @@
       <c r="D33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E33" s="2"/>
+      <c r="E33" s="2" t="n">
+        <v>-0.47</v>
+      </c>
       <c r="F33" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="G33" s="2"/>
+      <c r="G33" s="2" t="n">
+        <v>-0.65</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
@@ -1289,13 +1305,13 @@
         <v>16</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.52</v>
+        <v>0.29</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.5</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="37">
@@ -1312,13 +1328,13 @@
         <v>16</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>-0.12</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="38">
@@ -1354,13 +1370,13 @@
         <v>30</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="40">
@@ -1377,13 +1393,13 @@
         <v>30</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.25</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="41">
@@ -1400,13 +1416,13 @@
         <v>30</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="42">
@@ -1790,13 +1806,13 @@
         <v>30</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.43</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="60">
@@ -1813,13 +1829,13 @@
         <v>30</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="61">
@@ -1836,13 +1852,13 @@
         <v>30</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.39</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>-0.08</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_magallanes.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:05</t>
+    <t xml:space="preserve">2026-10-01 23:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_magallanes.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_magallanes.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:16</t>
+    <t xml:space="preserve">2026-10-05 19:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
